--- a/src/test/resources/testdata/CourseData.xlsx
+++ b/src/test/resources/testdata/CourseData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
-    <t>Extracted: 11-Jun-2026 14:31:00</t>
+    <t>Extracted: 11-Jun-2026 14:37:53</t>
   </si>
   <si>
     <t>S.No</t>
